--- a/scadenzario.xlsx
+++ b/scadenzario.xlsx
@@ -707,16 +707,44 @@
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Esempio</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Esempio</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Esempio</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
       <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>05/02/2029</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>esempio</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Esempio</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scadenzario.xlsx
+++ b/scadenzario.xlsx
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/scadenzario.xlsx
+++ b/scadenzario.xlsx
@@ -709,26 +709,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Esempio</t>
+          <t>Esempi</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Esempio</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Esempio</t>
-        </is>
-      </c>
+          <t>esem</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>05/08/2026</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/scadenzario.xlsx
+++ b/scadenzario.xlsx
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/scadenzario.xlsx
+++ b/scadenzario.xlsx
@@ -709,7 +709,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Esempi</t>
+          <t>Esempio</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/scadenzario.xlsx
+++ b/scadenzario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -742,6 +742,30 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Prova 2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>04/11/2026</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scadenzario.xlsx
+++ b/scadenzario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -709,7 +709,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Esempio</t>
+          <t>Prova 2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -743,28 +743,28 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Prova 2</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>04/08/2026</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>04/11/2026</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scadenzario.xlsx
+++ b/scadenzario.xlsx
@@ -707,40 +707,16 @@
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Prova 2</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>esem</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>05/08/2026</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>05/02/2029</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>esempio</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Esempio</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>

--- a/scadenzario.xlsx
+++ b/scadenzario.xlsx
@@ -707,14 +707,26 @@
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Esempio</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
       <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>05/12/2026</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
     </row>

--- a/scadenzario.xlsx
+++ b/scadenzario.xlsx
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/scadenzario.xlsx
+++ b/scadenzario.xlsx
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/scadenzario.xlsx
+++ b/scadenzario.xlsx
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/scadenzario.xlsx
+++ b/scadenzario.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/scadenzario.xlsx
+++ b/scadenzario.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/scadenzario.xlsx
+++ b/scadenzario.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/scadenzario.xlsx
+++ b/scadenzario.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/scadenzario.xlsx
+++ b/scadenzario.xlsx
@@ -480,11 +480,11 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>03/08/2027</t>
+          <t>03/04/2028</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>05/12/2026</t>
+          <t>05/07/2027</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>

--- a/scadenzario.xlsx
+++ b/scadenzario.xlsx
@@ -480,11 +480,11 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>03/04/2028</t>
+          <t>03/09/2027</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">

--- a/scadenzario.xlsx
+++ b/scadenzario.xlsx
@@ -731,14 +731,26 @@
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Prova 2</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
       <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>30/07/2027</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
     </row>
